--- a/analysis/forum_lect_api/forum_lect_analysis.xlsx
+++ b/analysis/forum_lect_api/forum_lect_analysis.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_work_KNOU\01_working_src\workspace_intellij\knou-lms-web-git\knou_dev_web\analysis\forum_lect_api\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21795" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="api_spec" sheetId="1" r:id="rId1"/>
@@ -20,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="232">
   <si>
     <t>category</t>
   </si>
@@ -713,12 +708,16 @@
   </si>
   <si>
     <t>기능 단위 JS 분리 및 모듈화</t>
+  </si>
+  <si>
+    <t>forum_score_manage</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -896,7 +895,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1079,6 +1078,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1342,7 +1353,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1353,6 +1364,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1456,7 +1473,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1491,7 +1508,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1668,7 +1685,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1677,7 +1694,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="20.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.25" bestFit="1" customWidth="1"/>
@@ -1692,7 +1709,7 @@
     <col min="11" max="11" width="58.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -1727,7 +1744,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A2" s="3" t="s">
         <v>21</v>
       </c>
@@ -1762,7 +1779,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
@@ -1797,7 +1814,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A4" s="3" t="s">
         <v>34</v>
       </c>
@@ -1832,8 +1849,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="54" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:11" ht="63" x14ac:dyDescent="0.6">
+      <c r="A5" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1867,8 +1884,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="27" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:11" ht="31.5" x14ac:dyDescent="0.6">
+      <c r="A6" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -1902,8 +1919,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A7" s="5" t="s">
         <v>59</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1937,8 +1954,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A8" s="4" t="s">
         <v>66</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -1972,8 +1989,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="27" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:11" ht="31.5" x14ac:dyDescent="0.6">
+      <c r="A9" s="4" t="s">
         <v>72</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -2007,8 +2024,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A10" s="4" t="s">
         <v>78</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -2042,8 +2059,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A11" s="4" t="s">
         <v>84</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -2077,8 +2094,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="54" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:11" ht="63" x14ac:dyDescent="0.6">
+      <c r="A12" s="4" t="s">
         <v>92</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -2112,8 +2129,8 @@
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:11" ht="47.25" x14ac:dyDescent="0.6">
+      <c r="A13" s="4" t="s">
         <v>98</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -2147,7 +2164,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="54" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="63" x14ac:dyDescent="0.6">
       <c r="A14" s="3" t="s">
         <v>108</v>
       </c>
@@ -2155,7 +2172,7 @@
         <v>99</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>100</v>
+        <v>231</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>101</v>
@@ -2182,7 +2199,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A15" s="3" t="s">
         <v>115</v>
       </c>
@@ -2217,7 +2234,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="47.25" x14ac:dyDescent="0.6">
       <c r="A16" s="3" t="s">
         <v>121</v>
       </c>
@@ -2252,7 +2269,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A17" s="3" t="s">
         <v>127</v>
       </c>
@@ -2287,7 +2304,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="47.25" x14ac:dyDescent="0.6">
       <c r="A18" s="3" t="s">
         <v>133</v>
       </c>
@@ -2322,7 +2339,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A19" s="3" t="s">
         <v>139</v>
       </c>
@@ -2357,7 +2374,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A20" s="3" t="s">
         <v>147</v>
       </c>
@@ -2392,7 +2409,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="47.25" x14ac:dyDescent="0.6">
       <c r="A21" s="3" t="s">
         <v>156</v>
       </c>
@@ -2427,7 +2444,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A22" s="2" t="s">
         <v>163</v>
       </c>
@@ -2462,7 +2479,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="47.25" x14ac:dyDescent="0.6">
       <c r="A23" s="3" t="s">
         <v>171</v>
       </c>
@@ -2497,7 +2514,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="47.25" x14ac:dyDescent="0.6">
       <c r="A24" s="3" t="s">
         <v>176</v>
       </c>
@@ -2532,7 +2549,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A25" s="3" t="s">
         <v>184</v>
       </c>
@@ -2567,7 +2584,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A26" s="3" t="s">
         <v>190</v>
       </c>
@@ -2602,7 +2619,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A27" s="3" t="s">
         <v>198</v>
       </c>
@@ -2647,7 +2664,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="6.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
@@ -2658,7 +2675,7 @@
     <col min="7" max="7" width="76.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>199</v>
       </c>
@@ -2681,7 +2698,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>206</v>
       </c>
@@ -2704,7 +2721,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>213</v>
       </c>
@@ -2727,7 +2744,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>219</v>
       </c>
@@ -2750,7 +2767,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>226</v>
       </c>
